--- a/salidas/empresas/VLO.xlsx
+++ b/salidas/empresas/VLO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>31.57822036743164</v>
+        <v>31.57822418212891</v>
       </c>
       <c r="C2" t="n">
         <v>57.06581497192383</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>27.24020957946777</v>
+        <v>27.24020767211914</v>
       </c>
       <c r="C3" t="n">
         <v>49.16819000244141</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>30.27365112304688</v>
+        <v>30.27366638183594</v>
       </c>
       <c r="C4" t="n">
         <v>54.64350891113281</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>32.78548812866211</v>
+        <v>32.78549575805664</v>
       </c>
       <c r="C5" t="n">
         <v>59.17733001708984</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.10856246948242</v>
+        <v>31.10854721069336</v>
       </c>
       <c r="C6" t="n">
         <v>56.07860946655273</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.73008346557617</v>
+        <v>33.73007965087891</v>
       </c>
       <c r="C7" t="n">
         <v>60.80438613891602</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.19151306152344</v>
+        <v>34.1915168762207</v>
       </c>
       <c r="C8" t="n">
         <v>61.63619613647461</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>29.14159202575684</v>
+        <v>29.14159774780273</v>
       </c>
       <c r="C9" t="n">
         <v>52.4680061340332</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>26.56758499145508</v>
+        <v>26.56758308410645</v>
       </c>
       <c r="C11" t="n">
         <v>47.83363723754883</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>28.00183296203613</v>
+        <v>28.00184440612793</v>
       </c>
       <c r="C12" t="n">
         <v>50.33820724487305</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>26.01368141174316</v>
+        <v>26.0136833190918</v>
       </c>
       <c r="C13" t="n">
         <v>46.76416778564453</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>27.60013198852539</v>
+        <v>27.60012626647949</v>
       </c>
       <c r="C14" t="n">
         <v>49.6160888671875</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>32.86257553100586</v>
+        <v>32.86257934570312</v>
       </c>
       <c r="C16" t="n">
         <v>58.94881057739258</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>35.78756332397461</v>
+        <v>35.78754425048828</v>
       </c>
       <c r="C17" t="n">
         <v>64.19561004638672</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>38.08649444580078</v>
+        <v>38.08651351928711</v>
       </c>
       <c r="C18" t="n">
         <v>68.20841217041016</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>37.69858551025391</v>
+        <v>37.69858169555664</v>
       </c>
       <c r="C19" t="n">
         <v>67.51371002197266</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>35.03582763671875</v>
+        <v>35.03580474853516</v>
       </c>
       <c r="C21" t="n">
         <v>62.6234016418457</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>34.35565948486328</v>
+        <v>34.35565567016602</v>
       </c>
       <c r="C22" t="n">
         <v>61.40767669677734</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>36.01770782470703</v>
+        <v>36.01768112182617</v>
       </c>
       <c r="C23" t="n">
         <v>64.37842559814453</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>33.34938430786133</v>
+        <v>33.34938049316406</v>
       </c>
       <c r="C24" t="n">
         <v>59.50639724731445</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>35.87492370605469</v>
+        <v>35.87490844726562</v>
       </c>
       <c r="C25" t="n">
         <v>64.01279449462891</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>29.65479850769043</v>
+        <v>29.6547966003418</v>
       </c>
       <c r="C27" t="n">
         <v>52.80621719360352</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>25.20939445495605</v>
+        <v>25.20940589904785</v>
       </c>
       <c r="C28" t="n">
         <v>44.89031219482422</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>25.07594680786133</v>
+        <v>25.07594871520996</v>
       </c>
       <c r="C29" t="n">
         <v>44.65265274047852</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>26.1762866973877</v>
+        <v>26.17629241943359</v>
       </c>
       <c r="C30" t="n">
         <v>46.47166442871094</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>21.20258712768555</v>
+        <v>21.20259475708008</v>
       </c>
       <c r="C31" t="n">
         <v>37.64168167114258</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.20199775695801</v>
+        <v>17.20199966430664</v>
       </c>
       <c r="C32" t="n">
         <v>30.53930473327637</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.97893333435059</v>
+        <v>17.97893524169922</v>
       </c>
       <c r="C33" t="n">
         <v>31.7733097076416</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>15.67208766937256</v>
+        <v>15.67208194732666</v>
       </c>
       <c r="C34" t="n">
         <v>27.6965274810791</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>10.64460277557373</v>
+        <v>10.64460372924805</v>
       </c>
       <c r="C35" t="n">
         <v>18.81170082092285</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>9.568096160888672</v>
+        <v>9.568092346191406</v>
       </c>
       <c r="C36" t="n">
         <v>16.7733097076416</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>11.28356838226318</v>
+        <v>11.28357219696045</v>
       </c>
       <c r="C37" t="n">
         <v>19.7806224822998</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>12.57669925689697</v>
+        <v>12.57669639587402</v>
       </c>
       <c r="C38" t="n">
         <v>22.04753112792969</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>10.16941165924072</v>
+        <v>10.16941452026367</v>
       </c>
       <c r="C39" t="n">
         <v>17.71480751037598</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.41079235076904</v>
+        <v>10.41079425811768</v>
       </c>
       <c r="C41" t="n">
         <v>18.13528251647949</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.82381725311279</v>
+        <v>11.82381248474121</v>
       </c>
       <c r="C42" t="n">
         <v>20.44789886474609</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>8.927321434020996</v>
+        <v>8.927322387695312</v>
       </c>
       <c r="C43" t="n">
         <v>15.43875694274902</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>9.986031532287598</v>
+        <v>9.986030578613281</v>
       </c>
       <c r="C45" t="n">
         <v>17.12979888916016</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>10.33240413665771</v>
+        <v>10.33240032196045</v>
       </c>
       <c r="C46" t="n">
         <v>17.72394943237305</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>9.644994735717773</v>
+        <v>9.64499568939209</v>
       </c>
       <c r="C47" t="n">
         <v>16.54479026794434</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>8.539633750915527</v>
+        <v>8.539637565612793</v>
       </c>
       <c r="C48" t="n">
         <v>14.52468013763428</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>9.001818656921387</v>
+        <v>9.001814842224121</v>
       </c>
       <c r="C49" t="n">
         <v>15.31078624725342</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>9.899311065673828</v>
+        <v>9.899306297302246</v>
       </c>
       <c r="C50" t="n">
         <v>16.83729362487793</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>9.441860198974609</v>
+        <v>9.44185733795166</v>
       </c>
       <c r="C51" t="n">
         <v>16.01462554931641</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>10.61670303344727</v>
+        <v>10.61670207977295</v>
       </c>
       <c r="C52" t="n">
         <v>18.0073127746582</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>11.20412349700928</v>
+        <v>11.20412445068359</v>
       </c>
       <c r="C53" t="n">
         <v>19.0036563873291</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>10.09207153320312</v>
+        <v>10.09207057952881</v>
       </c>
       <c r="C54" t="n">
         <v>17.07495307922363</v>
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>9.179033279418945</v>
+        <v>9.179031372070312</v>
       </c>
       <c r="C56" t="n">
         <v>15.53016471862793</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.545269966125488</v>
+        <v>8.545268058776855</v>
       </c>
       <c r="C57" t="n">
         <v>14.41499137878418</v>
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>9.726542472839355</v>
+        <v>9.726544380187988</v>
       </c>
       <c r="C59" t="n">
         <v>16.40767860412598</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>10.58209896087646</v>
+        <v>10.58209991455078</v>
       </c>
       <c r="C60" t="n">
         <v>17.80621528625488</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>12.55945491790771</v>
+        <v>12.5594482421875</v>
       </c>
       <c r="C61" t="n">
         <v>21.13345527648926</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>13.77627563476562</v>
+        <v>13.77628040313721</v>
       </c>
       <c r="C62" t="n">
         <v>23.18098640441895</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.33560657501221</v>
+        <v>15.33559894561768</v>
       </c>
       <c r="C63" t="n">
         <v>25.7586841583252</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>16.22809219360352</v>
+        <v>16.22809028625488</v>
       </c>
       <c r="C64" t="n">
         <v>27.25777053833008</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>15.40090560913086</v>
+        <v>15.40090942382812</v>
       </c>
       <c r="C65" t="n">
         <v>25.86837387084961</v>
@@ -1836,7 +1848,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>13.94136047363281</v>
+        <v>13.94135856628418</v>
       </c>
       <c r="C67" t="n">
         <v>23.37294387817383</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>13.69601535797119</v>
+        <v>13.69601154327393</v>
       </c>
       <c r="C68" t="n">
         <v>22.96160888671875</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>12.41718578338623</v>
+        <v>12.41718006134033</v>
       </c>
       <c r="C69" t="n">
         <v>20.76782417297363</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>9.717323303222656</v>
+        <v>9.717321395874023</v>
       </c>
       <c r="C70" t="n">
         <v>16.25228500366211</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>13.44465827941895</v>
+        <v>13.44466304779053</v>
       </c>
       <c r="C71" t="n">
         <v>22.48628807067871</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>12.24539947509766</v>
+        <v>12.24539661407471</v>
       </c>
       <c r="C72" t="n">
         <v>20.35648918151855</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.57456970214844</v>
+        <v>11.57456874847412</v>
       </c>
       <c r="C73" t="n">
         <v>19.2413158416748</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>13.19116306304932</v>
+        <v>13.19115829467773</v>
       </c>
       <c r="C74" t="n">
         <v>21.92870140075684</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>13.54800224304199</v>
+        <v>13.54800033569336</v>
       </c>
       <c r="C75" t="n">
         <v>22.38574028015137</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>14.25610637664795</v>
+        <v>14.25610446929932</v>
       </c>
       <c r="C76" t="n">
         <v>23.55575942993164</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>13.66417407989502</v>
+        <v>13.66417694091797</v>
       </c>
       <c r="C77" t="n">
         <v>22.57769775390625</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>11.75487232208252</v>
+        <v>11.7548713684082</v>
       </c>
       <c r="C78" t="n">
         <v>19.28701972961426</v>
@@ -2213,7 +2225,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>15.32033252716064</v>
+        <v>15.3203296661377</v>
       </c>
       <c r="C80" t="n">
         <v>25.13711166381836</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>17.52040481567383</v>
+        <v>17.52040672302246</v>
       </c>
       <c r="C81" t="n">
         <v>28.57403945922852</v>
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>16.30978202819824</v>
+        <v>16.30978775024414</v>
       </c>
       <c r="C83" t="n">
         <v>26.59963417053223</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>18.18929290771484</v>
+        <v>18.18930244445801</v>
       </c>
       <c r="C84" t="n">
         <v>29.48811721801758</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>19.23802947998047</v>
+        <v>19.23802757263184</v>
       </c>
       <c r="C85" t="n">
         <v>31.18829917907715</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>24.65646743774414</v>
+        <v>24.65647506713867</v>
       </c>
       <c r="C86" t="n">
         <v>39.97257614135742</v>
@@ -2445,7 +2457,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>25.7605152130127</v>
+        <v>25.76051712036133</v>
       </c>
       <c r="C88" t="n">
         <v>41.58135223388672</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>22.83278656005859</v>
+        <v>22.83279991149902</v>
       </c>
       <c r="C89" t="n">
         <v>36.85557556152344</v>
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>21.64581298828125</v>
+        <v>21.64581108093262</v>
       </c>
       <c r="C91" t="n">
         <v>34.77000045776367</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>22.26835823059082</v>
+        <v>22.26836204528809</v>
       </c>
       <c r="C92" t="n">
         <v>35.77000045776367</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>22.2538013458252</v>
+        <v>22.25380897521973</v>
       </c>
       <c r="C93" t="n">
         <v>35.52999877929688</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>21.38945770263672</v>
+        <v>21.38945388793945</v>
       </c>
       <c r="C94" t="n">
         <v>34.15000152587891</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>25.78634643554688</v>
+        <v>25.78634452819824</v>
       </c>
       <c r="C95" t="n">
         <v>41.16999816894531</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>28.78301239013672</v>
+        <v>28.78300666809082</v>
       </c>
       <c r="C96" t="n">
         <v>45.72000122070312</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.72929382324219</v>
+        <v>31.72930335998535</v>
       </c>
       <c r="C97" t="n">
         <v>50.40000152587891</v>
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.36124610900879</v>
+        <v>30.36126136779785</v>
       </c>
       <c r="C99" t="n">
         <v>47.97999954223633</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>33.60115432739258</v>
+        <v>33.60114288330078</v>
       </c>
       <c r="C100" t="n">
         <v>53.09999847412109</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>36.17659759521484</v>
+        <v>36.17661285400391</v>
       </c>
       <c r="C101" t="n">
         <v>57.16999816894531</v>
@@ -2880,7 +2892,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>31.84727096557617</v>
+        <v>31.84726524353027</v>
       </c>
       <c r="C103" t="n">
         <v>50.09999847412109</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>32.29225158691406</v>
+        <v>32.29225921630859</v>
       </c>
       <c r="C104" t="n">
         <v>50.79999923706055</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>34.59664916992188</v>
+        <v>34.59665298461914</v>
       </c>
       <c r="C105" t="n">
         <v>54.13999938964844</v>
@@ -2996,7 +3008,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>32.00860977172852</v>
+        <v>32.00861358642578</v>
       </c>
       <c r="C107" t="n">
         <v>50.09000015258789</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>31.23635673522949</v>
+        <v>31.23635864257812</v>
       </c>
       <c r="C108" t="n">
         <v>48.61000061035156</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>31.80825805664062</v>
+        <v>31.80826950073242</v>
       </c>
       <c r="C109" t="n">
         <v>49.5</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>33.9802360534668</v>
+        <v>33.980224609375</v>
       </c>
       <c r="C110" t="n">
         <v>52.88000106811523</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>39.93262100219727</v>
+        <v>39.93262481689453</v>
       </c>
       <c r="C111" t="n">
         <v>61.68999862670898</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>41.18191909790039</v>
+        <v>41.18193435668945</v>
       </c>
       <c r="C112" t="n">
         <v>63.61999893188477</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>36.83199310302734</v>
+        <v>36.83199691772461</v>
       </c>
       <c r="C113" t="n">
         <v>56.90000152587891</v>
@@ -3228,7 +3240,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>40.7978401184082</v>
+        <v>40.79783630371094</v>
       </c>
       <c r="C115" t="n">
         <v>62.59999847412109</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>43.02093505859375</v>
+        <v>43.02093124389648</v>
       </c>
       <c r="C116" t="n">
         <v>65.59999847412109</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>38.91556930541992</v>
+        <v>38.91557312011719</v>
       </c>
       <c r="C117" t="n">
         <v>59.34000015258789</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>39.41399765014648</v>
+        <v>39.41399002075195</v>
       </c>
       <c r="C118" t="n">
         <v>60.09999847412109</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>43.23078918457031</v>
+        <v>43.23079299926758</v>
       </c>
       <c r="C119" t="n">
         <v>65.91999816894531</v>
@@ -3402,7 +3414,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3431,7 +3443,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>44.82682418823242</v>
+        <v>44.82680511474609</v>
       </c>
       <c r="C122" t="n">
         <v>67.87000274658203</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>40.07077407836914</v>
+        <v>40.07077026367188</v>
       </c>
       <c r="C123" t="n">
         <v>60.08000183105469</v>
@@ -3518,7 +3530,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>39.26374053955078</v>
+        <v>39.26375198364258</v>
       </c>
       <c r="C125" t="n">
         <v>58.86999893188477</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>36.87672805786133</v>
+        <v>36.87673950195312</v>
       </c>
       <c r="C126" t="n">
         <v>54.70000076293945</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>34.38233184814453</v>
+        <v>34.3823356628418</v>
       </c>
       <c r="C127" t="n">
         <v>51</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.24525833129883</v>
+        <v>35.24525451660156</v>
       </c>
       <c r="C128" t="n">
         <v>52.27999877929688</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>37.73272705078125</v>
+        <v>37.73271560668945</v>
       </c>
       <c r="C129" t="n">
         <v>55.34999847412109</v>
@@ -3692,7 +3704,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>40.38458633422852</v>
+        <v>40.38457489013672</v>
       </c>
       <c r="C131" t="n">
         <v>59.2400016784668</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>42.35914993286133</v>
+        <v>42.35915756225586</v>
       </c>
       <c r="C132" t="n">
         <v>61.56000137329102</v>
@@ -3779,7 +3791,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>45.2491569519043</v>
+        <v>45.24916076660156</v>
       </c>
       <c r="C134" t="n">
         <v>65.76000213623047</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>47.24626159667969</v>
+        <v>47.24626922607422</v>
       </c>
       <c r="C135" t="n">
         <v>67.94999694824219</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>46.09205627441406</v>
+        <v>46.09204483032227</v>
       </c>
       <c r="C136" t="n">
         <v>66.29000091552734</v>
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>44.92393112182617</v>
+        <v>44.92392730712891</v>
       </c>
       <c r="C137" t="n">
         <v>64.61000061035156</v>
@@ -3924,7 +3936,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>47.4051628112793</v>
+        <v>47.40517044067383</v>
       </c>
       <c r="C139" t="n">
         <v>67.45999908447266</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>48.46627044677734</v>
+        <v>48.46625900268555</v>
       </c>
       <c r="C140" t="n">
         <v>68.97000122070312</v>
@@ -4011,7 +4023,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>54.61776733398438</v>
+        <v>54.61777877807617</v>
       </c>
       <c r="C142" t="n">
         <v>76.93000030517578</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>56.00930786132812</v>
+        <v>56.00930023193359</v>
       </c>
       <c r="C143" t="n">
         <v>78.88999938964844</v>
@@ -4098,7 +4110,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>65.80891418457031</v>
+        <v>65.80889892578125</v>
       </c>
       <c r="C145" t="n">
         <v>91.91000366210938</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>68.71591186523438</v>
+        <v>68.71590423583984</v>
       </c>
       <c r="C146" t="n">
         <v>95.97000122070312</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>65.33450317382812</v>
+        <v>65.33449554443359</v>
       </c>
       <c r="C147" t="n">
         <v>90.41999816894531</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>67.03253936767578</v>
+        <v>67.03254699707031</v>
       </c>
       <c r="C148" t="n">
         <v>92.76999664306641</v>
@@ -4243,7 +4255,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4272,7 +4284,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>80.63871002197266</v>
+        <v>80.63870239257812</v>
       </c>
       <c r="C151" t="n">
         <v>110.8300018310547</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>86.11016845703125</v>
+        <v>86.11016082763672</v>
       </c>
       <c r="C152" t="n">
         <v>118.3499984741211</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>86.36704254150391</v>
+        <v>86.36701965332031</v>
       </c>
       <c r="C153" t="n">
         <v>117.879997253418</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>83.34111022949219</v>
+        <v>83.34113311767578</v>
       </c>
       <c r="C154" t="n">
         <v>113.75</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>66.73883056640625</v>
+        <v>66.73885345458984</v>
       </c>
       <c r="C155" t="n">
         <v>91.08999633789062</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>59.10350036621094</v>
+        <v>59.10346984863281</v>
       </c>
       <c r="C156" t="n">
         <v>79.90000152587891</v>
@@ -4475,7 +4487,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>64.96206665039062</v>
+        <v>64.96205139160156</v>
       </c>
       <c r="C158" t="n">
         <v>87.81999969482422</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>60.99005889892578</v>
+        <v>60.99005126953125</v>
       </c>
       <c r="C159" t="n">
         <v>81.55999755859375</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>63.43536376953125</v>
+        <v>63.43534088134766</v>
       </c>
       <c r="C160" t="n">
         <v>84.83000183105469</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>67.79499053955078</v>
+        <v>67.79500579833984</v>
       </c>
       <c r="C161" t="n">
         <v>90.66000366210938</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>53.23320007324219</v>
+        <v>53.23317337036133</v>
       </c>
       <c r="C162" t="n">
         <v>70.40000152587891</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>64.73429107666016</v>
+        <v>64.73426055908203</v>
       </c>
       <c r="C163" t="n">
         <v>85.61000061035156</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>64.46204376220703</v>
+        <v>64.46207427978516</v>
       </c>
       <c r="C164" t="n">
         <v>85.25</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>57.55436325073242</v>
+        <v>57.55437850952148</v>
       </c>
       <c r="C165" t="n">
         <v>75.27999877929688</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>65.16916656494141</v>
+        <v>65.16915893554688</v>
       </c>
       <c r="C166" t="n">
         <v>85.23999786376953</v>
@@ -4765,7 +4777,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>73.66166687011719</v>
+        <v>73.66168212890625</v>
       </c>
       <c r="C168" t="n">
         <v>95.48999786376953</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>72.24230194091797</v>
+        <v>72.24229431152344</v>
       </c>
       <c r="C169" t="n">
         <v>93.65000152587891</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>65.03733825683594</v>
+        <v>65.03734588623047</v>
       </c>
       <c r="C170" t="n">
         <v>84.30999755859375</v>
@@ -4881,7 +4893,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>35.40224838256836</v>
+        <v>35.40225219726562</v>
       </c>
       <c r="C172" t="n">
         <v>45.36000061035156</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>49.44295120239258</v>
+        <v>49.44294357299805</v>
       </c>
       <c r="C173" t="n">
         <v>63.34999847412109</v>
@@ -4968,7 +4980,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>44.57566070556641</v>
+        <v>44.57566452026367</v>
       </c>
       <c r="C176" t="n">
         <v>56.22999954223633</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>42.42956924438477</v>
+        <v>42.42957305908203</v>
       </c>
       <c r="C177" t="n">
         <v>52.59000015258789</v>
@@ -5084,11 +5096,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>34.9505500793457</v>
+        <v>34.95055389404297</v>
       </c>
       <c r="C178" t="n">
         <v>43.31999969482422</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>31.15051460266113</v>
+        <v>31.1505241394043</v>
       </c>
       <c r="C179" t="n">
         <v>38.61000061035156</v>
@@ -5140,11 +5152,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>44.15895462036133</v>
+        <v>44.15896606445312</v>
       </c>
       <c r="C180" t="n">
         <v>53.77000045776367</v>
@@ -5167,7 +5179,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>46.34349060058594</v>
+        <v>46.34349822998047</v>
       </c>
       <c r="C182" t="n">
         <v>56.43000030517578</v>
@@ -5221,7 +5233,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5248,11 +5260,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>59.70787048339844</v>
+        <v>59.70790100097656</v>
       </c>
       <c r="C184" t="n">
         <v>71.59999847412109</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>61.6758918762207</v>
+        <v>61.67592239379883</v>
       </c>
       <c r="C185" t="n">
         <v>73.95999908447266</v>
@@ -5302,11 +5314,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>67.89385986328125</v>
+        <v>67.89387512207031</v>
       </c>
       <c r="C186" t="n">
         <v>80.40000152587891</v>
@@ -5329,11 +5341,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>65.93476104736328</v>
+        <v>65.93474578857422</v>
       </c>
       <c r="C187" t="n">
         <v>78.08000183105469</v>
@@ -5356,11 +5368,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>56.55289459228516</v>
+        <v>56.55289077758789</v>
       </c>
       <c r="C188" t="n">
         <v>66.97000122070312</v>
@@ -5383,7 +5395,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5410,11 +5422,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>60.45137786865234</v>
+        <v>60.45140075683594</v>
       </c>
       <c r="C190" t="n">
         <v>70.56999969482422</v>
@@ -5437,11 +5449,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>66.24210357666016</v>
+        <v>66.24209594726562</v>
       </c>
       <c r="C191" t="n">
         <v>77.33000183105469</v>
@@ -5464,11 +5476,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>58.07206726074219</v>
+        <v>58.07205581665039</v>
       </c>
       <c r="C192" t="n">
         <v>66.94000244140625</v>
@@ -5491,7 +5503,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5518,11 +5530,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>71.97847747802734</v>
+        <v>71.97844696044922</v>
       </c>
       <c r="C194" t="n">
         <v>82.97000122070312</v>
@@ -5545,7 +5557,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5574,11 +5586,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>89.09722900390625</v>
+        <v>89.09723663330078</v>
       </c>
       <c r="C196" t="n">
         <v>101.5400009155273</v>
@@ -5603,11 +5615,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>97.81916809082031</v>
+        <v>97.81917572021484</v>
       </c>
       <c r="C197" t="n">
         <v>111.4800033569336</v>
@@ -5632,11 +5644,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>114.6475143432617</v>
+        <v>114.6475219726562</v>
       </c>
       <c r="C198" t="n">
         <v>129.6000061035156</v>
@@ -5661,7 +5673,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5690,11 +5702,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>97.98999786376953</v>
+        <v>97.99000549316406</v>
       </c>
       <c r="C200" t="n">
         <v>110.7699966430664</v>
@@ -5719,11 +5731,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>104.5138473510742</v>
+        <v>104.5138626098633</v>
       </c>
       <c r="C201" t="n">
         <v>117.120002746582</v>
@@ -5748,11 +5760,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>95.34926605224609</v>
+        <v>95.34925842285156</v>
       </c>
       <c r="C202" t="n">
         <v>106.8499984741211</v>
@@ -5777,7 +5789,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5806,11 +5818,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>120.0741653442383</v>
+        <v>120.0741806030273</v>
       </c>
       <c r="C204" t="n">
         <v>133.6199951171875</v>
@@ -5835,7 +5847,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5864,11 +5876,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>125.8343505859375</v>
+        <v>125.834358215332</v>
       </c>
       <c r="C206" t="n">
         <v>140.0299987792969</v>
@@ -5893,11 +5905,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>119.2399978637695</v>
+        <v>119.2400054931641</v>
       </c>
       <c r="C207" t="n">
         <v>131.7299957275391</v>
@@ -5922,11 +5934,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>126.3638076782227</v>
+        <v>126.3638458251953</v>
       </c>
       <c r="C208" t="n">
         <v>139.6000061035156</v>
@@ -5951,11 +5963,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>103.7975540161133</v>
+        <v>103.7975616455078</v>
       </c>
       <c r="C209" t="n">
         <v>114.6699981689453</v>
@@ -5980,7 +5992,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6009,11 +6021,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>107.1605224609375</v>
+        <v>107.160530090332</v>
       </c>
       <c r="C211" t="n">
         <v>117.3000030517578</v>
@@ -6038,11 +6050,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>117.766960144043</v>
+        <v>117.7669525146484</v>
       </c>
       <c r="C212" t="n">
         <v>128.9100036621094</v>
@@ -6067,7 +6079,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6096,11 +6108,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>130.4941711425781</v>
+        <v>130.4941864013672</v>
       </c>
       <c r="C214" t="n">
         <v>141.7100067138672</v>
@@ -6125,11 +6137,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>116.9484024047852</v>
+        <v>116.9484100341797</v>
       </c>
       <c r="C215" t="n">
         <v>127</v>
@@ -6154,11 +6166,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>116.3750839233398</v>
+        <v>116.3750915527344</v>
       </c>
       <c r="C216" t="n">
         <v>125.3600006103516</v>
@@ -6183,11 +6195,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>120.6825332641602</v>
+        <v>120.6825180053711</v>
       </c>
       <c r="C217" t="n">
         <v>130</v>
@@ -6212,11 +6224,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>129.9244232177734</v>
+        <v>129.9243927001953</v>
       </c>
       <c r="C218" t="n">
         <v>138.8999938964844</v>
@@ -6241,7 +6253,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6270,7 +6282,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6299,7 +6311,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6328,11 +6340,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>148.0029449462891</v>
+        <v>148.0029296875</v>
       </c>
       <c r="C222" t="n">
         <v>157.1399993896484</v>
@@ -6357,7 +6369,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6386,11 +6398,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>152.3166351318359</v>
+        <v>152.3166046142578</v>
       </c>
       <c r="C224" t="n">
         <v>161.7200012207031</v>
@@ -6415,7 +6427,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6444,11 +6456,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>128.0255889892578</v>
+        <v>128.0256042480469</v>
       </c>
       <c r="C226" t="n">
         <v>135.0299987792969</v>
@@ -6473,11 +6485,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>123.0289688110352</v>
+        <v>123.0289764404297</v>
       </c>
       <c r="C227" t="n">
         <v>129.7599945068359</v>
@@ -6502,11 +6514,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>132.8666229248047</v>
+        <v>132.8666076660156</v>
       </c>
       <c r="C228" t="n">
         <v>139.0800018310547</v>
@@ -6531,7 +6543,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6560,11 +6572,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>128.0960083007812</v>
+        <v>128.0960235595703</v>
       </c>
       <c r="C230" t="n">
         <v>133</v>
@@ -6589,11 +6601,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>125.9097137451172</v>
+        <v>125.9097213745117</v>
       </c>
       <c r="C231" t="n">
         <v>130.7299957275391</v>
@@ -6618,11 +6630,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>127.200325012207</v>
+        <v>127.2003173828125</v>
       </c>
       <c r="C232" t="n">
         <v>132.0700073242188</v>
@@ -6647,7 +6659,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6676,11 +6688,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>125.2683944702148</v>
+        <v>125.2683792114258</v>
       </c>
       <c r="C234" t="n">
         <v>128.9700012207031</v>
@@ -6705,7 +6717,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6734,7 +6746,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6763,11 +6775,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>148.8539886474609</v>
+        <v>148.8539733886719</v>
       </c>
       <c r="C237" t="n">
         <v>152.0099945068359</v>
@@ -6792,11 +6804,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>166.72509765625</v>
+        <v>166.7250823974609</v>
       </c>
       <c r="C238" t="n">
         <v>170.2599945068359</v>
@@ -6821,7 +6833,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6850,7 +6862,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6879,7 +6891,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6908,7 +6920,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6937,11 +6949,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>202.8882446289062</v>
+        <v>202.8882293701172</v>
       </c>
       <c r="C243" t="n">
         <v>204.6399993896484</v>
@@ -6966,7 +6978,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6995,7 +7007,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7024,7 +7036,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7053,7 +7065,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7082,7 +7094,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7111,7 +7123,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7140,32 +7152,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>375.8399963378906</v>
+        <v>382.8599853515625</v>
       </c>
       <c r="C250" t="n">
-        <v>375.8399963378906</v>
+        <v>382.8599853515625</v>
       </c>
       <c r="D250" t="n">
-        <v>66073800</v>
+        <v>69798000</v>
       </c>
       <c r="E250" t="n">
         <v>24.03</v>
       </c>
       <c r="F250" t="n">
-        <v>15.64044928580486</v>
+        <v>15.93258366007335</v>
       </c>
       <c r="G250" t="n">
         <v>287927461</v>
       </c>
       <c r="H250" t="n">
-        <v>108214655887.8181</v>
+        <v>110235903500.7726</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2294807163252831</v>
+        <v>0.2424152241595323</v>
       </c>
     </row>
   </sheetData>
@@ -7197,75 +7209,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7301,13 +7313,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7343,13 +7355,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7385,13 +7397,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7427,13 +7439,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7469,13 +7481,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7502,7 +7514,7 @@
       <c r="I7" t="n">
         <v>-3.217550274223035</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7515,13 +7527,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7548,7 +7560,7 @@
       <c r="I8" t="n">
         <v>-3.939670932358318</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7561,13 +7573,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7594,7 +7606,7 @@
       <c r="I9" t="n">
         <v>-2.559414990859232</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7607,13 +7619,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7640,7 +7652,7 @@
       <c r="I10" t="n">
         <v>-1.069469835466179</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7653,13 +7665,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7686,7 +7698,7 @@
       <c r="I11" t="n">
         <v>0.5210237659963439</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7699,13 +7711,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7732,7 +7744,7 @@
       <c r="I12" t="n">
         <v>0.8592321755027424</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K12" t="n">
@@ -7745,13 +7757,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7778,7 +7790,7 @@
       <c r="I13" t="n">
         <v>1.106032906764169</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="K13" t="n">
@@ -7791,13 +7803,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7824,7 +7836,7 @@
       <c r="I14" t="n">
         <v>2.568555758683729</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="K14" t="n">
@@ -7837,13 +7849,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7870,7 +7882,7 @@
       <c r="I15" t="n">
         <v>3.345521023765996</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7883,13 +7895,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7916,7 +7928,7 @@
       <c r="I16" t="n">
         <v>2.477148080438757</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K16" t="n">
@@ -7929,13 +7941,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7962,7 +7974,7 @@
       <c r="I17" t="n">
         <v>2.659963436928702</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K17" t="n">
@@ -7975,13 +7987,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8008,7 +8020,7 @@
       <c r="I18" t="n">
         <v>1.837294332723949</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K18" t="n">
@@ -8021,13 +8033,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8054,7 +8066,7 @@
       <c r="I19" t="n">
         <v>3.427787934186471</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8067,13 +8079,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8100,7 +8112,7 @@
       <c r="I20" t="n">
         <v>5.320767824497257</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K20" t="n">
@@ -8113,13 +8125,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8146,7 +8158,7 @@
       <c r="I21" t="n">
         <v>4.799652650822669</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K21" t="n">
@@ -8159,13 +8171,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8192,7 +8204,7 @@
       <c r="I22" t="n">
         <v>4.2636197440585</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K22" t="n">
@@ -8205,13 +8217,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8238,7 +8250,7 @@
       <c r="I23" t="n">
         <v>4.98</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K23" t="n">
@@ -8251,13 +8263,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8284,7 +8296,7 @@
       <c r="I24" t="n">
         <v>5.34</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K24" t="n">
@@ -8297,13 +8309,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8330,7 +8342,7 @@
       <c r="I25" t="n">
         <v>5.59</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="K25" t="n">
@@ -8343,13 +8355,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8376,7 +8388,7 @@
       <c r="I26" t="n">
         <v>7.02</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K26" t="n">
@@ -8389,13 +8401,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8422,7 +8434,7 @@
       <c r="I27" t="n">
         <v>6.86</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K27" t="n">
@@ -8435,13 +8447,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8468,7 +8480,7 @@
       <c r="I28" t="n">
         <v>7.19</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K28" t="n">
@@ -8481,13 +8493,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8514,7 +8526,7 @@
       <c r="I29" t="n">
         <v>8.75</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K29" t="n">
@@ -8527,13 +8539,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8560,7 +8572,7 @@
       <c r="I30" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K30" t="n">
@@ -8573,13 +8585,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8606,7 +8618,7 @@
       <c r="I31" t="n">
         <v>7.94</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K31" t="n">
@@ -8619,13 +8631,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8652,7 +8664,7 @@
       <c r="I32" t="n">
         <v>7.12</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K32" t="n">
@@ -8665,13 +8677,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8698,7 +8710,7 @@
       <c r="I33" t="n">
         <v>6.19</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K33" t="n">
@@ -8711,13 +8723,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8744,7 +8756,7 @@
       <c r="I34" t="n">
         <v>4.73</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="K34" t="n">
@@ -8757,13 +8769,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8790,7 +8802,7 @@
       <c r="I35" t="n">
         <v>4.92</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K35" t="n">
@@ -8803,13 +8815,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8836,7 +8848,7 @@
       <c r="I36" t="n">
         <v>4.55</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="K36" t="n">
@@ -8849,13 +8861,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8882,7 +8894,7 @@
       <c r="I37" t="n">
         <v>4.050000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="K37" t="n">
@@ -8895,13 +8907,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8928,7 +8940,7 @@
       <c r="I38" t="n">
         <v>4.63</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K38" t="n">
@@ -8941,13 +8953,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8974,7 +8986,7 @@
       <c r="I39" t="n">
         <v>9.24</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K39" t="n">
@@ -8987,13 +8999,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43227</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9020,7 +9032,7 @@
       <c r="I40" t="n">
         <v>9.65</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43227</v>
       </c>
       <c r="K40" t="n">
@@ -9033,13 +9045,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9066,7 +9078,7 @@
       <c r="I41" t="n">
         <v>10.38</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K41" t="n">
@@ -9079,13 +9091,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9112,7 +9124,7 @@
       <c r="I42" t="n">
         <v>10.48</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="K42" t="n">
@@ -9125,13 +9137,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9158,7 +9170,7 @@
       <c r="I43" t="n">
         <v>7.3</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="K43" t="n">
@@ -9171,13 +9183,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9204,7 +9216,7 @@
       <c r="I44" t="n">
         <v>6.55</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="K44" t="n">
@@ -9217,13 +9229,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9250,7 +9262,7 @@
       <c r="I45" t="n">
         <v>6.06</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K45" t="n">
@@ -9263,13 +9275,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9296,7 +9308,7 @@
       <c r="I46" t="n">
         <v>5.53</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="K46" t="n">
@@ -9309,13 +9321,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9342,7 +9354,7 @@
       <c r="I47" t="n">
         <v>5.87</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="K47" t="n">
@@ -9355,13 +9367,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9388,7 +9400,7 @@
       <c r="I48" t="n">
         <v>0.9900000000000002</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K48" t="n">
@@ -9401,13 +9413,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9434,7 +9446,7 @@
       <c r="I49" t="n">
         <v>2.59</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K49" t="n">
@@ -9447,13 +9459,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9480,7 +9492,7 @@
       <c r="I50" t="n">
         <v>-0.03000000000000003</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K50" t="n">
@@ -9493,13 +9505,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9526,7 +9538,7 @@
       <c r="I51" t="n">
         <v>-3.49</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K51" t="n">
@@ -9539,13 +9551,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9572,7 +9584,7 @@
       <c r="I52" t="n">
         <v>-0.6800000000000002</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K52" t="n">
@@ -9585,13 +9597,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9618,7 +9630,7 @@
       <c r="I53" t="n">
         <v>-3.36</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9631,13 +9643,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9664,7 +9676,7 @@
       <c r="I54" t="n">
         <v>-1.09</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K54" t="n">
@@ -9677,13 +9689,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9710,7 +9722,7 @@
       <c r="I55" t="n">
         <v>2.27</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K55" t="n">
@@ -9723,13 +9735,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9756,7 +9768,7 @@
       <c r="I56" t="n">
         <v>6.21</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9769,13 +9781,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9802,7 +9814,7 @@
       <c r="I57" t="n">
         <v>17.39</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K57" t="n">
@@ -9815,13 +9827,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9848,7 +9860,7 @@
       <c r="I58" t="n">
         <v>23.45</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="K58" t="n">
@@ -9861,13 +9873,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,7 +9906,7 @@
       <c r="I59" t="n">
         <v>29.04</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9907,13 +9919,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9940,7 +9952,7 @@
       <c r="I60" t="n">
         <v>35.12</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9953,13 +9965,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9986,7 +9998,7 @@
       <c r="I61" t="n">
         <v>28.95</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -9999,13 +10011,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10032,7 +10044,7 @@
       <c r="I62" t="n">
         <v>29.25</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K62" t="n">
@@ -10045,13 +10057,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10078,7 +10090,7 @@
       <c r="I63" t="n">
         <v>24.92</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K63" t="n">
@@ -10091,13 +10103,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10124,7 +10136,7 @@
       <c r="I64" t="n">
         <v>20.38</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K64" t="n">
@@ -10137,13 +10149,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10170,7 +10182,7 @@
       <c r="I65" t="n">
         <v>17.69</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K65" t="n">
@@ -10183,13 +10195,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10216,7 +10228,7 @@
       <c r="I66" t="n">
         <v>11.34</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K66" t="n">
@@ -10229,13 +10241,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10262,7 +10274,7 @@
       <c r="I67" t="n">
         <v>8.58</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="K67" t="n">
@@ -10275,13 +10287,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10308,7 +10320,7 @@
       <c r="I68" t="n">
         <v>2.930000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K68" t="n">
@@ -10321,13 +10333,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10354,7 +10366,7 @@
       <c r="I69" t="n">
         <v>2.5</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K69" t="n">
@@ -10367,13 +10379,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10400,7 +10412,7 @@
       <c r="I70" t="n">
         <v>4.89</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="K70" t="n">
@@ -10413,13 +10425,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10446,7 +10458,7 @@
       <c r="I71" t="n">
         <v>7.57</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K71" t="n">
@@ -10459,13 +10471,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10492,7 +10504,7 @@
       <c r="I72" t="n">
         <v>13.69</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K72" t="n">
@@ -10505,13 +10517,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10538,7 +10550,7 @@
       <c r="I73" t="n">
         <v>24.03</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K73" t="n">
@@ -10575,52 +10587,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10649,10 +10661,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40477</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C7" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40599</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="C10" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="C11" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C13" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C14" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C15" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C17" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C18" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C19" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C20" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C21" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C22" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C23" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="C24" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C25" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C26" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C27" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C28" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C29" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C30" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="C31" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="C33" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="C34" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C35" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C36" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43227</v>
       </c>
       <c r="C37" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="C38" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="C39" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="C40" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="C41" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C42" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43767</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="C43" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="C44" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43941</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C45" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44032</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C46" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C47" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44246</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C48" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44309</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C49" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C50" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44491</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C51" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C52" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C53" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44764</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C54" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44855</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="C55" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C56" t="n">
@@ -12377,10 +12389,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C57" t="n">
@@ -12409,10 +12421,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C58" t="n">
@@ -12441,10 +12453,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C59" t="n">
@@ -12473,10 +12485,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C60" t="n">
@@ -12505,10 +12517,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C61" t="n">
@@ -12537,10 +12549,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C62" t="n">
@@ -12569,10 +12581,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C63" t="n">
@@ -12601,10 +12613,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45709</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="C64" t="n">
@@ -12633,10 +12645,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45764</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C65" t="n">
@@ -12665,10 +12677,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C66" t="n">
@@ -12697,10 +12709,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45947</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="C67" t="n">
@@ -12729,10 +12741,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C68" t="n">
@@ -12761,10 +12773,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C69" t="n">
@@ -12793,10 +12805,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46227</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C70" t="n">
@@ -12843,12 +12855,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/VLO.xlsx
+++ b/salidas/empresas/VLO.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>31.57822418212891</v>
+        <v>31.57821846008301</v>
       </c>
       <c r="C2" t="n">
         <v>57.06581497192383</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>27.24020767211914</v>
+        <v>27.24021148681641</v>
       </c>
       <c r="C3" t="n">
         <v>49.16819000244141</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>30.27366638183594</v>
+        <v>30.27365684509277</v>
       </c>
       <c r="C4" t="n">
         <v>54.64350891113281</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>32.78549575805664</v>
+        <v>32.78548812866211</v>
       </c>
       <c r="C5" t="n">
         <v>59.17733001708984</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.10854721069336</v>
+        <v>31.10856437683105</v>
       </c>
       <c r="C6" t="n">
         <v>56.07860946655273</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.73007965087891</v>
+        <v>33.73008728027344</v>
       </c>
       <c r="C7" t="n">
         <v>60.80438613891602</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.1915168762207</v>
+        <v>34.19152069091797</v>
       </c>
       <c r="C8" t="n">
         <v>61.63619613647461</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>29.14159774780273</v>
+        <v>29.1415958404541</v>
       </c>
       <c r="C9" t="n">
         <v>52.4680061340332</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>26.13097381591797</v>
+        <v>26.1309700012207</v>
       </c>
       <c r="C10" t="n">
         <v>47.04753112792969</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>26.56758308410645</v>
+        <v>26.56759643554688</v>
       </c>
       <c r="C11" t="n">
         <v>47.83363723754883</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>28.00184440612793</v>
+        <v>28.00181770324707</v>
       </c>
       <c r="C12" t="n">
         <v>50.33820724487305</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>26.0136833190918</v>
+        <v>26.01368522644043</v>
       </c>
       <c r="C13" t="n">
         <v>46.76416778564453</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>27.60012626647949</v>
+        <v>27.60012817382812</v>
       </c>
       <c r="C14" t="n">
         <v>49.6160888671875</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>29.32103538513184</v>
+        <v>29.32102012634277</v>
       </c>
       <c r="C15" t="n">
         <v>52.59597778320312</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>32.86257934570312</v>
+        <v>32.86259460449219</v>
       </c>
       <c r="C16" t="n">
         <v>58.94881057739258</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>38.08651351928711</v>
+        <v>38.08649444580078</v>
       </c>
       <c r="C18" t="n">
         <v>68.20841217041016</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>37.69858169555664</v>
+        <v>37.69858932495117</v>
       </c>
       <c r="C19" t="n">
         <v>67.51371002197266</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>34.20229721069336</v>
+        <v>34.20231246948242</v>
       </c>
       <c r="C20" t="n">
         <v>61.25228500366211</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>35.03580474853516</v>
+        <v>35.03582000732422</v>
       </c>
       <c r="C21" t="n">
         <v>62.6234016418457</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>34.35565567016602</v>
+        <v>34.35565948486328</v>
       </c>
       <c r="C22" t="n">
         <v>61.40767669677734</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>36.01768112182617</v>
+        <v>36.01769256591797</v>
       </c>
       <c r="C23" t="n">
         <v>64.37842559814453</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>35.87490844726562</v>
+        <v>35.87491989135742</v>
       </c>
       <c r="C25" t="n">
         <v>64.01279449462891</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>30.25522994995117</v>
+        <v>30.25521469116211</v>
       </c>
       <c r="C26" t="n">
         <v>53.98537445068359</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>29.6547966003418</v>
+        <v>29.65480422973633</v>
       </c>
       <c r="C27" t="n">
         <v>52.80621719360352</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>25.20940589904785</v>
+        <v>25.20940399169922</v>
       </c>
       <c r="C28" t="n">
         <v>44.89031219482422</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>26.17629241943359</v>
+        <v>26.17628860473633</v>
       </c>
       <c r="C30" t="n">
         <v>46.47166442871094</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>21.20259475708008</v>
+        <v>21.20259094238281</v>
       </c>
       <c r="C31" t="n">
         <v>37.64168167114258</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.20199966430664</v>
+        <v>17.20200729370117</v>
       </c>
       <c r="C32" t="n">
         <v>30.53930473327637</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.97893524169922</v>
+        <v>17.97894287109375</v>
       </c>
       <c r="C33" t="n">
         <v>31.7733097076416</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>15.67208194732666</v>
+        <v>15.67208099365234</v>
       </c>
       <c r="C34" t="n">
         <v>27.6965274810791</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>10.64460372924805</v>
+        <v>10.6446008682251</v>
       </c>
       <c r="C35" t="n">
         <v>18.81170082092285</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>9.568092346191406</v>
+        <v>9.56809139251709</v>
       </c>
       <c r="C36" t="n">
         <v>16.7733097076416</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>11.28357219696045</v>
+        <v>11.28357601165771</v>
       </c>
       <c r="C37" t="n">
         <v>19.7806224822998</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>9.392802238464355</v>
+        <v>9.392805099487305</v>
       </c>
       <c r="C40" t="n">
         <v>16.36197471618652</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.41079425811768</v>
+        <v>10.41079235076904</v>
       </c>
       <c r="C41" t="n">
         <v>18.13528251647949</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.82381248474121</v>
+        <v>11.82380962371826</v>
       </c>
       <c r="C42" t="n">
         <v>20.44789886474609</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>8.927322387695312</v>
+        <v>8.927323341369629</v>
       </c>
       <c r="C43" t="n">
         <v>15.43875694274902</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>9.986030578613281</v>
+        <v>9.986031532287598</v>
       </c>
       <c r="C45" t="n">
         <v>17.12979888916016</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>10.33240032196045</v>
+        <v>10.33239841461182</v>
       </c>
       <c r="C46" t="n">
         <v>17.72394943237305</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>9.64499568939209</v>
+        <v>9.644989967346191</v>
       </c>
       <c r="C47" t="n">
         <v>16.54479026794434</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>8.539637565612793</v>
+        <v>8.539632797241211</v>
       </c>
       <c r="C48" t="n">
         <v>14.52468013763428</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>9.001814842224121</v>
+        <v>9.001815795898438</v>
       </c>
       <c r="C49" t="n">
         <v>15.31078624725342</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>9.899306297302246</v>
+        <v>9.899309158325195</v>
       </c>
       <c r="C50" t="n">
         <v>16.83729362487793</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>9.44185733795166</v>
+        <v>9.441860198974609</v>
       </c>
       <c r="C51" t="n">
         <v>16.01462554931641</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>10.61670207977295</v>
+        <v>10.61670303344727</v>
       </c>
       <c r="C52" t="n">
         <v>18.0073127746582</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>11.20412445068359</v>
+        <v>11.20411968231201</v>
       </c>
       <c r="C53" t="n">
         <v>19.0036563873291</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>9.713890075683594</v>
+        <v>9.713887214660645</v>
       </c>
       <c r="C55" t="n">
         <v>16.43510055541992</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>9.179031372070312</v>
+        <v>9.179027557373047</v>
       </c>
       <c r="C56" t="n">
         <v>15.53016471862793</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.545268058776855</v>
+        <v>8.545269012451172</v>
       </c>
       <c r="C57" t="n">
         <v>14.41499137878418</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.488118171691895</v>
+        <v>9.488119125366211</v>
       </c>
       <c r="C58" t="n">
         <v>16.00548362731934</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>9.726544380187988</v>
+        <v>9.726542472839355</v>
       </c>
       <c r="C59" t="n">
         <v>16.40767860412598</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>10.58209991455078</v>
+        <v>10.58209705352783</v>
       </c>
       <c r="C60" t="n">
         <v>17.80621528625488</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>12.5594482421875</v>
+        <v>12.55944728851318</v>
       </c>
       <c r="C61" t="n">
         <v>21.13345527648926</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>13.77628040313721</v>
+        <v>13.77628517150879</v>
       </c>
       <c r="C62" t="n">
         <v>23.18098640441895</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>15.40090942382812</v>
+        <v>15.40091037750244</v>
       </c>
       <c r="C65" t="n">
         <v>25.86837387084961</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>14.99364471435547</v>
+        <v>14.9936466217041</v>
       </c>
       <c r="C66" t="n">
         <v>25.13711166381836</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>13.94135856628418</v>
+        <v>13.94137001037598</v>
       </c>
       <c r="C67" t="n">
         <v>23.37294387817383</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>13.69601154327393</v>
+        <v>13.69600963592529</v>
       </c>
       <c r="C68" t="n">
         <v>22.96160888671875</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>12.41718006134033</v>
+        <v>12.41717910766602</v>
       </c>
       <c r="C69" t="n">
         <v>20.76782417297363</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>9.717321395874023</v>
+        <v>9.717319488525391</v>
       </c>
       <c r="C70" t="n">
         <v>16.25228500366211</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>13.44466304779053</v>
+        <v>13.44465732574463</v>
       </c>
       <c r="C71" t="n">
         <v>22.48628807067871</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.57456874847412</v>
+        <v>11.57456684112549</v>
       </c>
       <c r="C73" t="n">
         <v>19.2413158416748</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>13.19115829467773</v>
+        <v>13.19115352630615</v>
       </c>
       <c r="C74" t="n">
         <v>21.92870140075684</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>13.54800033569336</v>
+        <v>13.54799842834473</v>
       </c>
       <c r="C75" t="n">
         <v>22.38574028015137</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>14.25610446929932</v>
+        <v>14.25610828399658</v>
       </c>
       <c r="C76" t="n">
         <v>23.55575942993164</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>11.7548713684082</v>
+        <v>11.7548770904541</v>
       </c>
       <c r="C78" t="n">
         <v>19.28701972961426</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>13.45403575897217</v>
+        <v>13.4540433883667</v>
       </c>
       <c r="C79" t="n">
         <v>22.07495307922363</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>15.3203296661377</v>
+        <v>15.32033348083496</v>
       </c>
       <c r="C80" t="n">
         <v>25.13711166381836</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>17.52040672302246</v>
+        <v>17.52040481567383</v>
       </c>
       <c r="C81" t="n">
         <v>28.57403945922852</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>17.75580596923828</v>
+        <v>17.75580024719238</v>
       </c>
       <c r="C82" t="n">
         <v>28.95795249938965</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>16.30978775024414</v>
+        <v>16.30978584289551</v>
       </c>
       <c r="C83" t="n">
         <v>26.59963417053223</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>18.18930244445801</v>
+        <v>18.18930053710938</v>
       </c>
       <c r="C84" t="n">
         <v>29.48811721801758</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>19.23802757263184</v>
+        <v>19.23802947998047</v>
       </c>
       <c r="C85" t="n">
         <v>31.18829917907715</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>24.65647506713867</v>
+        <v>24.65646553039551</v>
       </c>
       <c r="C86" t="n">
         <v>39.97257614135742</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>25.81714057922363</v>
+        <v>25.81713676452637</v>
       </c>
       <c r="C87" t="n">
         <v>41.67276000976562</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>25.76051712036133</v>
+        <v>25.76051330566406</v>
       </c>
       <c r="C88" t="n">
         <v>41.58135223388672</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>22.83279991149902</v>
+        <v>22.83279609680176</v>
       </c>
       <c r="C89" t="n">
         <v>36.85557556152344</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.29391288757324</v>
+        <v>25.29391098022461</v>
       </c>
       <c r="C90" t="n">
         <v>40.63000106811523</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>21.64581108093262</v>
+        <v>21.64580917358398</v>
       </c>
       <c r="C91" t="n">
         <v>34.77000045776367</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>22.26836204528809</v>
+        <v>22.26835823059082</v>
       </c>
       <c r="C92" t="n">
         <v>35.77000045776367</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>22.25380897521973</v>
+        <v>22.2538013458252</v>
       </c>
       <c r="C93" t="n">
         <v>35.52999877929688</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>25.78634452819824</v>
+        <v>25.78635215759277</v>
       </c>
       <c r="C95" t="n">
         <v>41.16999816894531</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>28.78300666809082</v>
+        <v>28.78301048278809</v>
       </c>
       <c r="C96" t="n">
         <v>45.72000122070312</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.72930335998535</v>
+        <v>31.72929000854492</v>
       </c>
       <c r="C97" t="n">
         <v>50.40000152587891</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>32.16998672485352</v>
+        <v>32.16998291015625</v>
       </c>
       <c r="C98" t="n">
         <v>51.09999847412109</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.36126136779785</v>
+        <v>30.36126708984375</v>
       </c>
       <c r="C99" t="n">
         <v>47.97999954223633</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>36.17661285400391</v>
+        <v>36.17659378051758</v>
       </c>
       <c r="C101" t="n">
         <v>57.16999816894531</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>35.62954711914062</v>
+        <v>35.62954330444336</v>
       </c>
       <c r="C102" t="n">
         <v>56.04999923706055</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>31.84726524353027</v>
+        <v>31.84727096557617</v>
       </c>
       <c r="C103" t="n">
         <v>50.09999847412109</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>32.29225921630859</v>
+        <v>32.29225158691406</v>
       </c>
       <c r="C104" t="n">
         <v>50.79999923706055</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>29.56755256652832</v>
+        <v>29.56754875183105</v>
       </c>
       <c r="C106" t="n">
         <v>46.27000045776367</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>31.23635864257812</v>
+        <v>31.23636627197266</v>
       </c>
       <c r="C108" t="n">
         <v>48.61000061035156</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>31.80826950073242</v>
+        <v>31.80827331542969</v>
       </c>
       <c r="C109" t="n">
         <v>49.5</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>39.93262481689453</v>
+        <v>39.9326171875</v>
       </c>
       <c r="C111" t="n">
         <v>61.68999862670898</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>41.18193435668945</v>
+        <v>41.18193054199219</v>
       </c>
       <c r="C112" t="n">
         <v>63.61999893188477</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>38.60805892944336</v>
+        <v>38.60805130004883</v>
       </c>
       <c r="C114" t="n">
         <v>59.2400016784668</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>40.79783630371094</v>
+        <v>40.79783248901367</v>
       </c>
       <c r="C115" t="n">
         <v>62.59999847412109</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>38.91557312011719</v>
+        <v>38.91557693481445</v>
       </c>
       <c r="C117" t="n">
         <v>59.34000015258789</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>39.41399002075195</v>
+        <v>39.41400527954102</v>
       </c>
       <c r="C118" t="n">
         <v>60.09999847412109</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>43.23079299926758</v>
+        <v>43.23078536987305</v>
       </c>
       <c r="C119" t="n">
         <v>65.91999816894531</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>47.46213150024414</v>
+        <v>47.46214294433594</v>
       </c>
       <c r="C120" t="n">
         <v>71.86000061035156</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>46.70256805419922</v>
+        <v>46.70258331298828</v>
       </c>
       <c r="C121" t="n">
         <v>70.70999908447266</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>44.82680511474609</v>
+        <v>44.82681274414062</v>
       </c>
       <c r="C122" t="n">
         <v>67.87000274658203</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>40.07077026367188</v>
+        <v>40.07076644897461</v>
       </c>
       <c r="C123" t="n">
         <v>60.08000183105469</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>42.77861022949219</v>
+        <v>42.77861785888672</v>
       </c>
       <c r="C124" t="n">
         <v>64.13999938964844</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>36.87673950195312</v>
+        <v>36.87673187255859</v>
       </c>
       <c r="C126" t="n">
         <v>54.70000076293945</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>34.3823356628418</v>
+        <v>34.38233184814453</v>
       </c>
       <c r="C127" t="n">
         <v>51</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.24525451660156</v>
+        <v>35.24525833129883</v>
       </c>
       <c r="C128" t="n">
         <v>52.27999877929688</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>37.73271560668945</v>
+        <v>37.73271942138672</v>
       </c>
       <c r="C129" t="n">
         <v>55.34999847412109</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>36.13070297241211</v>
+        <v>36.13069915771484</v>
       </c>
       <c r="C130" t="n">
         <v>53</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>40.38457489013672</v>
+        <v>40.38458251953125</v>
       </c>
       <c r="C131" t="n">
         <v>59.2400016784668</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>42.35915756225586</v>
+        <v>42.35916137695312</v>
       </c>
       <c r="C132" t="n">
         <v>61.56000137329102</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>47.01067352294922</v>
+        <v>47.01068496704102</v>
       </c>
       <c r="C133" t="n">
         <v>68.31999969482422</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>45.24916076660156</v>
+        <v>45.24916458129883</v>
       </c>
       <c r="C134" t="n">
         <v>65.76000213623047</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>47.24626922607422</v>
+        <v>47.24626159667969</v>
       </c>
       <c r="C135" t="n">
         <v>67.94999694824219</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>46.09204483032227</v>
+        <v>46.092041015625</v>
       </c>
       <c r="C136" t="n">
         <v>66.29000091552734</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>44.92392730712891</v>
+        <v>44.92391586303711</v>
       </c>
       <c r="C137" t="n">
         <v>64.61000061035156</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>48.46625900268555</v>
+        <v>48.46627426147461</v>
       </c>
       <c r="C140" t="n">
         <v>68.97000122070312</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>48.3487548828125</v>
+        <v>48.34875106811523</v>
       </c>
       <c r="C141" t="n">
         <v>68.09999847412109</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>54.61777877807617</v>
+        <v>54.61777114868164</v>
       </c>
       <c r="C142" t="n">
         <v>76.93000030517578</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>61.30516815185547</v>
+        <v>61.30515670776367</v>
       </c>
       <c r="C144" t="n">
         <v>85.62000274658203</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>65.80889892578125</v>
+        <v>65.80890655517578</v>
       </c>
       <c r="C145" t="n">
         <v>91.91000366210938</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>68.71590423583984</v>
+        <v>68.71591949462891</v>
       </c>
       <c r="C146" t="n">
         <v>95.97000122070312</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>65.33449554443359</v>
+        <v>65.33451843261719</v>
       </c>
       <c r="C147" t="n">
         <v>90.41999816894531</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>67.03254699707031</v>
+        <v>67.03253936767578</v>
       </c>
       <c r="C148" t="n">
         <v>92.76999664306641</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>80.15435028076172</v>
+        <v>80.15432739257812</v>
       </c>
       <c r="C149" t="n">
         <v>110.9300003051758</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>88.18379211425781</v>
+        <v>88.18380737304688</v>
       </c>
       <c r="C150" t="n">
         <v>121.1999969482422</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>80.63870239257812</v>
+        <v>80.63871002197266</v>
       </c>
       <c r="C151" t="n">
         <v>110.8300018310547</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>86.11016082763672</v>
+        <v>86.11017608642578</v>
       </c>
       <c r="C152" t="n">
         <v>118.3499984741211</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>86.36701965332031</v>
+        <v>86.36705017089844</v>
       </c>
       <c r="C153" t="n">
         <v>117.879997253418</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>83.34113311767578</v>
+        <v>83.34112548828125</v>
       </c>
       <c r="C154" t="n">
         <v>113.75</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>66.73885345458984</v>
+        <v>66.73883056640625</v>
       </c>
       <c r="C155" t="n">
         <v>91.08999633789062</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>59.10346984863281</v>
+        <v>59.10349655151367</v>
       </c>
       <c r="C156" t="n">
         <v>79.90000152587891</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>55.45668792724609</v>
+        <v>55.45666885375977</v>
       </c>
       <c r="C157" t="n">
         <v>74.97000122070312</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>60.99005126953125</v>
+        <v>60.99004745483398</v>
       </c>
       <c r="C159" t="n">
         <v>81.55999755859375</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>63.43534088134766</v>
+        <v>63.43535614013672</v>
       </c>
       <c r="C160" t="n">
         <v>84.83000183105469</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>67.79500579833984</v>
+        <v>67.79498291015625</v>
       </c>
       <c r="C161" t="n">
         <v>90.66000366210938</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>53.23317337036133</v>
+        <v>53.23318862915039</v>
       </c>
       <c r="C162" t="n">
         <v>70.40000152587891</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>64.73426055908203</v>
+        <v>64.73426818847656</v>
       </c>
       <c r="C163" t="n">
         <v>85.61000061035156</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>64.46207427978516</v>
+        <v>64.46206665039062</v>
       </c>
       <c r="C164" t="n">
         <v>85.25</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>57.55437850952148</v>
+        <v>57.55437469482422</v>
       </c>
       <c r="C165" t="n">
         <v>75.27999877929688</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>65.16915893554688</v>
+        <v>65.16916656494141</v>
       </c>
       <c r="C166" t="n">
         <v>85.23999786376953</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>74.14482879638672</v>
+        <v>74.14484405517578</v>
       </c>
       <c r="C167" t="n">
         <v>96.98000335693359</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>73.66168212890625</v>
+        <v>73.66166687011719</v>
       </c>
       <c r="C168" t="n">
         <v>95.48999786376953</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>72.24229431152344</v>
+        <v>72.24227905273438</v>
       </c>
       <c r="C169" t="n">
         <v>93.65000152587891</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>65.03734588623047</v>
+        <v>65.03732299804688</v>
       </c>
       <c r="C170" t="n">
         <v>84.30999755859375</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>51.70632171630859</v>
+        <v>51.70631790161133</v>
       </c>
       <c r="C171" t="n">
         <v>66.25</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>35.40225219726562</v>
+        <v>35.40225601196289</v>
       </c>
       <c r="C172" t="n">
         <v>45.36000061035156</v>
@@ -4984,7 +4984,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>52.82806396484375</v>
+        <v>52.82806015014648</v>
       </c>
       <c r="C174" t="n">
         <v>66.63999938964844</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>46.62885284423828</v>
+        <v>46.62884902954102</v>
       </c>
       <c r="C175" t="n">
         <v>58.81999969482422</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>42.42957305908203</v>
+        <v>42.42958068847656</v>
       </c>
       <c r="C177" t="n">
         <v>52.59000015258789</v>
@@ -5100,7 +5100,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>34.95055389404297</v>
+        <v>34.95054626464844</v>
       </c>
       <c r="C178" t="n">
         <v>43.31999969482422</v>
@@ -5156,7 +5156,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>44.15896606445312</v>
+        <v>44.15895843505859</v>
       </c>
       <c r="C180" t="n">
         <v>53.77000045776367</v>
@@ -5183,7 +5183,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>46.45847702026367</v>
+        <v>46.45846939086914</v>
       </c>
       <c r="C181" t="n">
         <v>56.56999969482422</v>
@@ -5210,7 +5210,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>46.34349822998047</v>
+        <v>46.343505859375</v>
       </c>
       <c r="C182" t="n">
         <v>56.43000030517578</v>
@@ -5264,7 +5264,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>59.70790100097656</v>
+        <v>59.70787811279297</v>
       </c>
       <c r="C184" t="n">
         <v>71.59999847412109</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>61.67592239379883</v>
+        <v>61.67589950561523</v>
       </c>
       <c r="C185" t="n">
         <v>73.95999908447266</v>
@@ -5318,7 +5318,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>67.89387512207031</v>
+        <v>67.89386749267578</v>
       </c>
       <c r="C186" t="n">
         <v>80.40000152587891</v>
@@ -5345,7 +5345,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>65.93474578857422</v>
+        <v>65.93476104736328</v>
       </c>
       <c r="C187" t="n">
         <v>78.08000183105469</v>
@@ -5399,7 +5399,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>56.80219268798828</v>
+        <v>56.80220413208008</v>
       </c>
       <c r="C189" t="n">
         <v>66.30999755859375</v>
@@ -5426,7 +5426,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>60.45140075683594</v>
+        <v>60.45138931274414</v>
       </c>
       <c r="C190" t="n">
         <v>70.56999969482422</v>
@@ -5480,7 +5480,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>58.07205581665039</v>
+        <v>58.07205963134766</v>
       </c>
       <c r="C192" t="n">
         <v>66.94000244140625</v>
@@ -5507,7 +5507,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>65.15972900390625</v>
+        <v>65.15971374511719</v>
       </c>
       <c r="C193" t="n">
         <v>75.11000061035156</v>
@@ -5590,7 +5590,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>89.09723663330078</v>
+        <v>89.09722137451172</v>
       </c>
       <c r="C196" t="n">
         <v>101.5400009155273</v>
@@ -5648,7 +5648,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>114.6475219726562</v>
+        <v>114.6475143432617</v>
       </c>
       <c r="C198" t="n">
         <v>129.6000061035156</v>
@@ -5677,7 +5677,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>94.01803588867188</v>
+        <v>94.01802062988281</v>
       </c>
       <c r="C199" t="n">
         <v>106.2799987792969</v>
@@ -5735,7 +5735,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>104.5138626098633</v>
+        <v>104.5138549804688</v>
       </c>
       <c r="C201" t="n">
         <v>117.120002746582</v>
@@ -5764,7 +5764,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>95.34925842285156</v>
+        <v>95.34927368164062</v>
       </c>
       <c r="C202" t="n">
         <v>106.8499984741211</v>
@@ -5793,7 +5793,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>112.0365142822266</v>
+        <v>112.0364990234375</v>
       </c>
       <c r="C203" t="n">
         <v>125.5500030517578</v>
@@ -5851,7 +5851,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>113.9994735717773</v>
+        <v>113.9994583129883</v>
       </c>
       <c r="C205" t="n">
         <v>126.8600006103516</v>
@@ -5880,7 +5880,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>125.834358215332</v>
+        <v>125.8343353271484</v>
       </c>
       <c r="C206" t="n">
         <v>140.0299987792969</v>
@@ -5909,7 +5909,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>119.2400054931641</v>
+        <v>119.2400283813477</v>
       </c>
       <c r="C207" t="n">
         <v>131.7299957275391</v>
@@ -5938,7 +5938,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>126.3638458251953</v>
+        <v>126.3638229370117</v>
       </c>
       <c r="C208" t="n">
         <v>139.6000061035156</v>
@@ -5996,7 +5996,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>97.78739929199219</v>
+        <v>97.78740692138672</v>
       </c>
       <c r="C210" t="n">
         <v>107.0400009155273</v>
@@ -6025,7 +6025,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>107.160530090332</v>
+        <v>107.1605224609375</v>
       </c>
       <c r="C211" t="n">
         <v>117.3000030517578</v>
@@ -6054,7 +6054,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>117.7669525146484</v>
+        <v>117.766960144043</v>
       </c>
       <c r="C212" t="n">
         <v>128.9100036621094</v>
@@ -6083,7 +6083,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>119.6188812255859</v>
+        <v>119.618896484375</v>
       </c>
       <c r="C213" t="n">
         <v>129.8999938964844</v>
@@ -6170,7 +6170,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>116.3750915527344</v>
+        <v>116.3750839233398</v>
       </c>
       <c r="C216" t="n">
         <v>125.3600006103516</v>
@@ -6199,7 +6199,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>120.6825180053711</v>
+        <v>120.6825332641602</v>
       </c>
       <c r="C217" t="n">
         <v>130</v>
@@ -6257,7 +6257,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>132.3189849853516</v>
+        <v>132.3189697265625</v>
       </c>
       <c r="C219" t="n">
         <v>141.4600067138672</v>
@@ -6286,7 +6286,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>159.66015625</v>
+        <v>159.6601715087891</v>
       </c>
       <c r="C220" t="n">
         <v>170.6900024414062</v>
@@ -6315,7 +6315,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>149.5393371582031</v>
+        <v>149.5393218994141</v>
       </c>
       <c r="C221" t="n">
         <v>159.8699951171875</v>
@@ -6460,7 +6460,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>128.0256042480469</v>
+        <v>128.0256195068359</v>
       </c>
       <c r="C226" t="n">
         <v>135.0299987792969</v>
@@ -6489,7 +6489,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>123.0289764404297</v>
+        <v>123.0289611816406</v>
       </c>
       <c r="C227" t="n">
         <v>129.7599945068359</v>
@@ -6547,7 +6547,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>117.1133041381836</v>
+        <v>117.1133193969727</v>
       </c>
       <c r="C229" t="n">
         <v>122.5899963378906</v>
@@ -6605,7 +6605,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>125.9097213745117</v>
+        <v>125.9097137451172</v>
       </c>
       <c r="C231" t="n">
         <v>130.7299957275391</v>
@@ -6634,7 +6634,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>127.2003173828125</v>
+        <v>127.2003021240234</v>
       </c>
       <c r="C232" t="n">
         <v>132.0700073242188</v>
@@ -6663,7 +6663,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>111.8095245361328</v>
+        <v>111.8095321655273</v>
       </c>
       <c r="C233" t="n">
         <v>116.0899963378906</v>
@@ -6692,7 +6692,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>125.2683792114258</v>
+        <v>125.2683868408203</v>
       </c>
       <c r="C234" t="n">
         <v>128.9700012207031</v>
@@ -6779,7 +6779,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>148.8539733886719</v>
+        <v>148.85400390625</v>
       </c>
       <c r="C237" t="n">
         <v>152.0099945068359</v>
@@ -6808,7 +6808,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>166.7250823974609</v>
+        <v>166.72509765625</v>
       </c>
       <c r="C238" t="n">
         <v>170.2599945068359</v>
@@ -6837,7 +6837,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>166.0396423339844</v>
+        <v>166.0396270751953</v>
       </c>
       <c r="C239" t="n">
         <v>169.5599975585938</v>
@@ -6895,7 +6895,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>160.4153900146484</v>
+        <v>160.4154052734375</v>
       </c>
       <c r="C241" t="n">
         <v>162.7899932861328</v>
@@ -6924,7 +6924,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>178.7834930419922</v>
+        <v>178.7835083007812</v>
       </c>
       <c r="C242" t="n">
         <v>181.4299926757812</v>
@@ -6953,7 +6953,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>202.8882293701172</v>
+        <v>202.8882446289062</v>
       </c>
       <c r="C243" t="n">
         <v>204.6399993896484</v>
